--- a/flights_sample.xlsx
+++ b/flights_sample.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الرحلات" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'الرحلات'!$1:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,9 +28,10 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="12"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -38,10 +41,28 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A7A3C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="005D4037"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +71,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="003F51B5"/>
+        <fgColor rgb="000D2137"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F5"/>
+        <fgColor rgb="001E3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE8E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
       </patternFill>
     </fill>
     <fill>
@@ -65,16 +101,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00EEF2FF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -83,47 +114,72 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="medium">
+        <color rgb="001E3A5F"/>
+      </left>
+      <right style="medium">
+        <color rgb="001E3A5F"/>
+      </right>
+      <top style="medium">
+        <color rgb="001E3A5F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001E3A5F"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00B0BEC5"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00B0BEC5"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00B0BEC5"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00B0BEC5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0BEC5"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0BEC5"/>
+      </right>
+      <top style="medium">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00F9A825"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -491,373 +547,644 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="50" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>✈  نموذج رفع الرحلات  |  Flight Upload Template</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="54" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>مكان الانطلاق
-(A) origin</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
+origin  (A)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>الوجهة
-(B) destination</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
+destination  (B)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>التاريخ
-(C) date
+date  (C)
 dd/MM/yyyy</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>السعر $
-(D) price</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
+price  (D)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>عدد المقاعد
-(E) availableSeats</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
+totalSeats  (E)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>رقم الرحلة
-(F) flightNumber</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
+flightNumber  (F)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>وقت الإقلاع
-(G) departureTime</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
+departureTime  (G)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>وقت الوصول
-(H) arrivalTime</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
+arrivalTime  (H)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>وقت الصعود
-(I) boardingTime</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
+boardingTime  (I)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>مدة الرحلة
-(J) duration</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+duration  (J)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="52" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>🔴 إلزامي</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>🔴 إلزامي</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>🔴 إلزامي
+مثال: 15/08/2026</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>🔴 إلزامي
+مثال: 350</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>🔴 إلزامي
+يجب أن يكون
+مضاعف 6 للمقاعد</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>🟢 اختياري
+مثال: SV205</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>🟢 اختياري
+تنسيق: HH:mm</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>🟢 اختياري
+تنسيق: HH:mm</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>🟢 اختياري
+تنسيق: HH:mm</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>🟢 اختياري
+مثال: 3س 30د</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>⚠  تنبيه: عدد المقاعد (E) يتحكم في خريطة الاختيار البصرية — يُنصح باستخدام مضاعفات 6 (مثل 24 أو 30 أو 36 أو 48) لصفوف كاملة.  الأعمدة F-J اختيارية لكن تُعرض للعميل في تفاصيل الرحلة والتذكرة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>القاهرة</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>دبي</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>15/08/2026</t>
         </is>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <v>350</v>
       </c>
-      <c r="E2" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="E5" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>EG101</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>13:45</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>3س 30د</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>الرياض</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>لندن</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>20/08/2026</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E6" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>SV205</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>6س 30د</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>الكويت</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>باريس</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>950</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>KU312</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>5س 30د</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>أبوظبي</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>إسطنبول</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>600</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>EY418</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>4س 30د</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>عمّان</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>فرانكفورت</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="E9" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>SV205</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>6س 30د</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>الكويت</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>باريس</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>950</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>KU312</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>RJ521</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>4س 30د</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>بيروت</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>مدريد</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>850</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>ME630</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>5س 30د</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>أبوظبي</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>إسطنبول</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>25/08/2026</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>600</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>EY418</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>4س 30د</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>دبي</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>نيويورك</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>EK201</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>06:15</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>14س 30د</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>كوالالمبور</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>750</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>QR851</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>7س 00د</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>مسقط</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>بانكوك</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>900</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>WY301</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>01:15</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>8س 30د</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>الدار البيضاء</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>القاهرة</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>450</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>AT721</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>05:45</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>4س 30د</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>عمّان</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>فرانكفورت</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>01/09/2026</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>RJ521</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>4س 30د</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>بيروت</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>مدريد</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>05/09/2026</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>850</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>ME630</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>4س 30د</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A4:J4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>